--- a/importationFileUpload/Template-Ar.xlsx
+++ b/importationFileUpload/Template-Ar.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Houda\Documents\SDL3\importationFileUpload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\31-07-2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF9D4A1-6A0F-43D6-97FD-07E33819ACDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66FD439E-6CE9-489D-8EEB-3C2C8E917CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Arabe" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Arabe!$A$1:$AF$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Arabe!$A$1:$AG$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
   <si>
     <t>العدد</t>
   </si>
@@ -169,6 +169,36 @@
   </si>
   <si>
     <t>طبيعة تاريخ ميلاد الزوج(ة)</t>
+  </si>
+  <si>
+    <t>رقم التعريف الوطني</t>
+  </si>
+  <si>
+    <t>خضرة</t>
+  </si>
+  <si>
+    <t>تومي</t>
+  </si>
+  <si>
+    <t>مفترض</t>
+  </si>
+  <si>
+    <t>سلمانة</t>
+  </si>
+  <si>
+    <t>زهرة</t>
+  </si>
+  <si>
+    <t>محمد</t>
+  </si>
+  <si>
+    <t>ذكر</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>نقطة الحالة العائلية</t>
   </si>
 </sst>
 </file>
@@ -370,13 +400,17 @@
       <alignment horizontal="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -388,6 +422,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
@@ -397,13 +434,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Currency" xfId="5" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -696,618 +730,677 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AF15"/>
+  <dimension ref="A1:AG15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
     <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" customWidth="1"/>
-    <col min="8" max="8" width="23.140625" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="20" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="51.85546875" customWidth="1"/>
-    <col min="18" max="18" width="24.85546875" customWidth="1"/>
-    <col min="19" max="19" width="22.28515625" customWidth="1"/>
-    <col min="20" max="20" width="26" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="26" customWidth="1"/>
-    <col min="22" max="22" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="34.85546875" customWidth="1"/>
-    <col min="24" max="24" width="34.7109375" customWidth="1"/>
-    <col min="25" max="25" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="18.28515625" customWidth="1"/>
-    <col min="28" max="28" width="16" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="22.42578125" customWidth="1"/>
-    <col min="30" max="30" width="34.7109375" customWidth="1"/>
-    <col min="31" max="31" width="23.140625" customWidth="1"/>
-    <col min="32" max="32" width="47.5703125" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" customWidth="1"/>
+    <col min="7" max="7" width="20.85546875" style="4" customWidth="1"/>
+    <col min="8" max="9" width="23.140625" customWidth="1"/>
+    <col min="10" max="10" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="15" customWidth="1"/>
+    <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="51.85546875" customWidth="1"/>
+    <col min="19" max="19" width="24.85546875" customWidth="1"/>
+    <col min="20" max="20" width="22.28515625" customWidth="1"/>
+    <col min="21" max="21" width="26" style="4" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="26" customWidth="1"/>
+    <col min="23" max="23" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="34.85546875" customWidth="1"/>
+    <col min="25" max="25" width="34.7109375" customWidth="1"/>
+    <col min="26" max="26" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="18.28515625" customWidth="1"/>
+    <col min="29" max="29" width="16" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="22.42578125" customWidth="1"/>
+    <col min="31" max="31" width="34.7109375" customWidth="1"/>
+    <col min="32" max="32" width="23.140625" customWidth="1"/>
+    <col min="33" max="33" width="47.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="1" customFormat="1" ht="54" thickTop="1" thickBot="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:33" s="14" customFormat="1" ht="54" thickTop="1" thickBot="1">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="T1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="U1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="V1" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="V1" s="9" t="s">
+      <c r="W1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="W1" s="7" t="s">
+      <c r="X1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Z1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="AA1" s="7" t="s">
+      <c r="AB1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="9" t="s">
+      <c r="AC1" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AD1" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="AF1" s="11" t="s">
+      <c r="AG1" s="13" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:32" s="12" customFormat="1" ht="27.75" thickTop="1" thickBot="1">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
-      <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="3"/>
-      <c r="AB2" s="3"/>
-      <c r="AC2" s="3"/>
-      <c r="AD2" s="3"/>
-      <c r="AE2" s="3"/>
-      <c r="AF2" s="3"/>
+    <row r="2" spans="1:33" s="2" customFormat="1" ht="27.75" thickTop="1" thickBot="1">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1875</v>
+      </c>
+      <c r="C2" s="3">
+        <v>38091</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="3">
+        <v>25933</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1">
+        <v>472</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" s="1">
+        <v>1</v>
+      </c>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1">
+        <v>1</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="U2" s="3">
+        <v>27759</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="W2" s="1">
+        <v>55</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
     </row>
-    <row r="3" spans="1:32" ht="27.75" thickTop="1" thickBot="1">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
+    <row r="3" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
       <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
-      <c r="AB3" s="3"/>
-      <c r="AC3" s="3"/>
-      <c r="AD3" s="3"/>
-      <c r="AE3" s="3"/>
-      <c r="AF3" s="3"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
+      <c r="Z3" s="1"/>
+      <c r="AA3" s="1"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="1"/>
+      <c r="AD3" s="1"/>
+      <c r="AE3" s="1"/>
+      <c r="AF3" s="1"/>
+      <c r="AG3" s="1"/>
     </row>
-    <row r="4" spans="1:32" ht="27.75" thickTop="1" thickBot="1">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
+    <row r="4" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
       <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
-      <c r="AB4" s="3"/>
-      <c r="AC4" s="3"/>
-      <c r="AD4" s="3"/>
-      <c r="AE4" s="3"/>
-      <c r="AF4" s="3"/>
+      <c r="V4" s="1"/>
+      <c r="W4" s="1"/>
+      <c r="X4" s="1"/>
+      <c r="Y4" s="1"/>
+      <c r="Z4" s="1"/>
+      <c r="AA4" s="1"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="1"/>
+      <c r="AD4" s="1"/>
+      <c r="AE4" s="1"/>
+      <c r="AF4" s="1"/>
+      <c r="AG4" s="1"/>
     </row>
-    <row r="5" spans="1:32" ht="27.75" thickTop="1" thickBot="1">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
+    <row r="5" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
       <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="3"/>
-      <c r="AA5" s="3"/>
-      <c r="AB5" s="3"/>
-      <c r="AC5" s="3"/>
-      <c r="AD5" s="3"/>
-      <c r="AE5" s="3"/>
-      <c r="AF5" s="3"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
+      <c r="Y5" s="1"/>
+      <c r="Z5" s="1"/>
+      <c r="AA5" s="1"/>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="1"/>
+      <c r="AD5" s="1"/>
+      <c r="AE5" s="1"/>
+      <c r="AF5" s="1"/>
+      <c r="AG5" s="1"/>
     </row>
-    <row r="6" spans="1:32" ht="27.75" thickTop="1" thickBot="1">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
+    <row r="6" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
       <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
       <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="3"/>
-      <c r="AA6" s="3"/>
-      <c r="AB6" s="3"/>
-      <c r="AC6" s="3"/>
-      <c r="AD6" s="3"/>
-      <c r="AE6" s="3"/>
-      <c r="AF6" s="3"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="1"/>
+      <c r="Z6" s="1"/>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="1"/>
+      <c r="AD6" s="1"/>
+      <c r="AE6" s="1"/>
+      <c r="AF6" s="1"/>
+      <c r="AG6" s="1"/>
     </row>
-    <row r="7" spans="1:32" ht="27.75" thickTop="1" thickBot="1">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
+    <row r="7" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
       <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
       <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="3"/>
-      <c r="AA7" s="3"/>
-      <c r="AB7" s="3"/>
-      <c r="AC7" s="3"/>
-      <c r="AD7" s="3"/>
-      <c r="AE7" s="3"/>
-      <c r="AF7" s="3"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="1"/>
+      <c r="Z7" s="1"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="1"/>
+      <c r="AC7" s="1"/>
+      <c r="AD7" s="1"/>
+      <c r="AE7" s="1"/>
+      <c r="AF7" s="1"/>
+      <c r="AG7" s="1"/>
     </row>
-    <row r="8" spans="1:32" ht="27.75" thickTop="1" thickBot="1">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
+    <row r="8" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
       <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
       <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
-      <c r="AA8" s="3"/>
-      <c r="AB8" s="3"/>
-      <c r="AC8" s="3"/>
-      <c r="AD8" s="3"/>
-      <c r="AE8" s="3"/>
-      <c r="AF8" s="3"/>
+      <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
+      <c r="X8" s="1"/>
+      <c r="Y8" s="1"/>
+      <c r="Z8" s="1"/>
+      <c r="AA8" s="1"/>
+      <c r="AB8" s="1"/>
+      <c r="AC8" s="1"/>
+      <c r="AD8" s="1"/>
+      <c r="AE8" s="1"/>
+      <c r="AF8" s="1"/>
+      <c r="AG8" s="1"/>
     </row>
-    <row r="9" spans="1:32" ht="27.75" thickTop="1" thickBot="1">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
+    <row r="9" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
       <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
       <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
-      <c r="AA9" s="3"/>
-      <c r="AB9" s="3"/>
-      <c r="AC9" s="3"/>
-      <c r="AD9" s="3"/>
-      <c r="AE9" s="3"/>
-      <c r="AF9" s="3"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
+      <c r="AD9" s="1"/>
+      <c r="AE9" s="1"/>
+      <c r="AF9" s="1"/>
+      <c r="AG9" s="1"/>
     </row>
-    <row r="10" spans="1:32" ht="27.75" thickTop="1" thickBot="1">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
+    <row r="10" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
       <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
       <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="3"/>
-      <c r="AA10" s="3"/>
-      <c r="AB10" s="3"/>
-      <c r="AC10" s="3"/>
-      <c r="AD10" s="3"/>
-      <c r="AE10" s="3"/>
-      <c r="AF10" s="3"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1"/>
+      <c r="Y10" s="1"/>
+      <c r="Z10" s="1"/>
+      <c r="AA10" s="1"/>
+      <c r="AB10" s="1"/>
+      <c r="AC10" s="1"/>
+      <c r="AD10" s="1"/>
+      <c r="AE10" s="1"/>
+      <c r="AF10" s="1"/>
+      <c r="AG10" s="1"/>
     </row>
-    <row r="11" spans="1:32" ht="27.75" thickTop="1" thickBot="1">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
+    <row r="11" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
       <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
       <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
-      <c r="AA11" s="3"/>
-      <c r="AB11" s="3"/>
-      <c r="AC11" s="3"/>
-      <c r="AD11" s="3"/>
-      <c r="AE11" s="3"/>
-      <c r="AF11" s="3"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
+      <c r="Z11" s="1"/>
+      <c r="AA11" s="1"/>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="1"/>
+      <c r="AD11" s="1"/>
+      <c r="AE11" s="1"/>
+      <c r="AF11" s="1"/>
+      <c r="AG11" s="1"/>
     </row>
-    <row r="12" spans="1:32" ht="27.75" thickTop="1" thickBot="1">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
+    <row r="12" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
       <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
-      <c r="AA12" s="3"/>
-      <c r="AB12" s="3"/>
-      <c r="AC12" s="3"/>
-      <c r="AD12" s="3"/>
-      <c r="AE12" s="3"/>
-      <c r="AF12" s="3"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1"/>
+      <c r="Y12" s="1"/>
+      <c r="Z12" s="1"/>
+      <c r="AA12" s="1"/>
+      <c r="AB12" s="1"/>
+      <c r="AC12" s="1"/>
+      <c r="AD12" s="1"/>
+      <c r="AE12" s="1"/>
+      <c r="AF12" s="1"/>
+      <c r="AG12" s="1"/>
     </row>
-    <row r="13" spans="1:32" ht="27.75" thickTop="1" thickBot="1">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
+    <row r="13" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
       <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
       <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
-      <c r="AA13" s="3"/>
-      <c r="AB13" s="3"/>
-      <c r="AC13" s="3"/>
-      <c r="AD13" s="3"/>
-      <c r="AE13" s="3"/>
-      <c r="AF13" s="3"/>
+      <c r="V13" s="1"/>
+      <c r="W13" s="1"/>
+      <c r="X13" s="1"/>
+      <c r="Y13" s="1"/>
+      <c r="Z13" s="1"/>
+      <c r="AA13" s="1"/>
+      <c r="AB13" s="1"/>
+      <c r="AC13" s="1"/>
+      <c r="AD13" s="1"/>
+      <c r="AE13" s="1"/>
+      <c r="AF13" s="1"/>
+      <c r="AG13" s="1"/>
     </row>
-    <row r="14" spans="1:32" ht="27.75" thickTop="1" thickBot="1">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
+    <row r="14" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
       <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
       <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
-      <c r="AA14" s="3"/>
-      <c r="AB14" s="3"/>
-      <c r="AC14" s="3"/>
-      <c r="AD14" s="3"/>
-      <c r="AE14" s="3"/>
-      <c r="AF14" s="3"/>
+      <c r="V14" s="1"/>
+      <c r="W14" s="1"/>
+      <c r="X14" s="1"/>
+      <c r="Y14" s="1"/>
+      <c r="Z14" s="1"/>
+      <c r="AA14" s="1"/>
+      <c r="AB14" s="1"/>
+      <c r="AC14" s="1"/>
+      <c r="AD14" s="1"/>
+      <c r="AE14" s="1"/>
+      <c r="AF14" s="1"/>
+      <c r="AG14" s="1"/>
     </row>
-    <row r="15" spans="1:32" ht="27" thickTop="1">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
+    <row r="15" spans="1:33" ht="27" thickTop="1">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
       <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
       <c r="U15" s="3"/>
-      <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="3"/>
-      <c r="AA15" s="3"/>
-      <c r="AB15" s="3"/>
-      <c r="AC15" s="3"/>
-      <c r="AD15" s="3"/>
-      <c r="AE15" s="3"/>
-      <c r="AF15" s="3"/>
+      <c r="V15" s="1"/>
+      <c r="W15" s="1"/>
+      <c r="X15" s="1"/>
+      <c r="Y15" s="1"/>
+      <c r="Z15" s="1"/>
+      <c r="AA15" s="1"/>
+      <c r="AB15" s="1"/>
+      <c r="AC15" s="1"/>
+      <c r="AD15" s="1"/>
+      <c r="AE15" s="1"/>
+      <c r="AF15" s="1"/>
+      <c r="AG15" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AF1" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD86">
+  <autoFilter ref="A1:AG1" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AE86">
       <sortCondition ref="C1"/>
     </sortState>
   </autoFilter>

--- a/importationFileUpload/Template-Ar.xlsx
+++ b/importationFileUpload/Template-Ar.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27726"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\31-07-2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moknial01\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66FD439E-6CE9-489D-8EEB-3C2C8E917CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Arabe" sheetId="2" r:id="rId1"/>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>العدد</t>
   </si>
@@ -173,40 +172,13 @@
   <si>
     <t>رقم التعريف الوطني</t>
   </si>
-  <si>
-    <t>خضرة</t>
-  </si>
-  <si>
-    <t>تومي</t>
-  </si>
-  <si>
-    <t>مفترض</t>
-  </si>
-  <si>
-    <t>سلمانة</t>
-  </si>
-  <si>
-    <t>زهرة</t>
-  </si>
-  <si>
-    <t>محمد</t>
-  </si>
-  <si>
-    <t>ذكر</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>نقطة الحالة العائلية</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -394,23 +366,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyFont="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyFont="0">
       <alignment horizontal="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -422,9 +390,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
@@ -434,24 +399,27 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="12">
-    <cellStyle name="Currency" xfId="5" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="Currency 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Currency" xfId="5"/>
+    <cellStyle name="Currency 2" xfId="9"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal 2 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Normal 2 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="Normal 2 4" xfId="10" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Normal 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Style 1" xfId="2" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="Style 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="Style 2 2" xfId="11" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="Style 6" xfId="4" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Normal 2" xfId="6"/>
+    <cellStyle name="Normal 2 2" xfId="7"/>
+    <cellStyle name="Normal 2 3" xfId="1"/>
+    <cellStyle name="Normal 2 4" xfId="10"/>
+    <cellStyle name="Normal 3" xfId="3"/>
+    <cellStyle name="Style 1" xfId="2"/>
+    <cellStyle name="Style 2" xfId="8"/>
+    <cellStyle name="Style 2 2" xfId="11"/>
+    <cellStyle name="Style 6" xfId="4"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -728,18 +696,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AG15"/>
+  <dimension ref="A1:CM15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" customWidth="1"/>
     <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" customWidth="1"/>
-    <col min="7" max="7" width="20.85546875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
     <col min="8" max="9" width="23.140625" customWidth="1"/>
     <col min="10" max="10" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.140625" bestFit="1" customWidth="1"/>
@@ -750,7 +718,7 @@
     <col min="17" max="18" width="51.85546875" customWidth="1"/>
     <col min="19" max="19" width="24.85546875" customWidth="1"/>
     <col min="20" max="20" width="22.28515625" customWidth="1"/>
-    <col min="21" max="21" width="26" style="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="26" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="26" customWidth="1"/>
     <col min="23" max="23" width="22.85546875" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="34.85546875" customWidth="1"/>
@@ -765,642 +733,658 @@
     <col min="33" max="33" width="47.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="14" customFormat="1" ht="54" thickTop="1" thickBot="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:91" s="1" customFormat="1" ht="54" thickTop="1" thickBot="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="T1" s="7" t="s">
+      <c r="T1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="U1" s="11" t="s">
+      <c r="U1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="11" t="s">
+      <c r="V1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="W1" s="12" t="s">
+      <c r="W1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="X1" s="10" t="s">
+      <c r="X1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Y1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="7" t="s">
+      <c r="Z1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AA1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="AB1" s="10" t="s">
+      <c r="AB1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="12" t="s">
+      <c r="AC1" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AD1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AF1" s="7" t="s">
+      <c r="AF1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="AG1" s="13" t="s">
+      <c r="AG1" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:33" s="2" customFormat="1" ht="27.75" thickTop="1" thickBot="1">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1875</v>
-      </c>
-      <c r="C2" s="3">
-        <v>38091</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G2" s="3">
-        <v>25933</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1">
-        <v>472</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="M2" s="1">
-        <v>1</v>
-      </c>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1">
-        <v>1</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="U2" s="3">
-        <v>27759</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="W2" s="1">
-        <v>55</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y2" s="1"/>
-      <c r="Z2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB2" s="1"/>
-      <c r="AC2" s="1"/>
-      <c r="AD2" s="1"/>
-      <c r="AE2" s="1"/>
-      <c r="AF2" s="1"/>
-      <c r="AG2" s="1"/>
+    <row r="2" spans="1:91" s="12" customFormat="1" ht="27.75" thickTop="1" thickBot="1">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
+      <c r="AB2" s="3"/>
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="3"/>
+      <c r="AE2" s="3"/>
+      <c r="AF2" s="3"/>
+      <c r="AG2" s="3"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="1"/>
+      <c r="AW2" s="1"/>
+      <c r="AX2" s="1"/>
+      <c r="AY2" s="1"/>
+      <c r="AZ2" s="1"/>
+      <c r="BA2" s="1"/>
+      <c r="BB2" s="1"/>
+      <c r="BC2" s="1"/>
+      <c r="BD2" s="1"/>
+      <c r="BE2" s="1"/>
+      <c r="BF2" s="1"/>
+      <c r="BG2" s="1"/>
+      <c r="BH2" s="1"/>
+      <c r="BI2" s="1"/>
+      <c r="BJ2" s="1"/>
+      <c r="BK2" s="1"/>
+      <c r="BL2" s="1"/>
+      <c r="BM2" s="1"/>
+      <c r="BN2" s="1"/>
+      <c r="BO2" s="1"/>
+      <c r="BP2" s="1"/>
+      <c r="BQ2" s="1"/>
+      <c r="BR2" s="1"/>
+      <c r="BS2" s="1"/>
+      <c r="BT2" s="1"/>
+      <c r="BU2" s="1"/>
+      <c r="BV2" s="1"/>
+      <c r="BW2" s="1"/>
+      <c r="BX2" s="1"/>
+      <c r="BY2" s="1"/>
+      <c r="BZ2" s="1"/>
+      <c r="CA2" s="1"/>
+      <c r="CB2" s="1"/>
+      <c r="CC2" s="1"/>
+      <c r="CD2" s="1"/>
+      <c r="CE2" s="1"/>
+      <c r="CF2" s="1"/>
+      <c r="CG2" s="1"/>
+      <c r="CH2" s="1"/>
+      <c r="CI2" s="1"/>
+      <c r="CJ2" s="1"/>
+      <c r="CK2" s="1"/>
+      <c r="CL2" s="1"/>
+      <c r="CM2" s="1"/>
     </row>
-    <row r="3" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
+    <row r="3" spans="1:91" ht="27.75" thickTop="1" thickBot="1">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
-      <c r="T3" s="1"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
       <c r="U3" s="3"/>
-      <c r="V3" s="1"/>
-      <c r="W3" s="1"/>
-      <c r="X3" s="1"/>
-      <c r="Y3" s="1"/>
-      <c r="Z3" s="1"/>
-      <c r="AA3" s="1"/>
-      <c r="AB3" s="1"/>
-      <c r="AC3" s="1"/>
-      <c r="AD3" s="1"/>
-      <c r="AE3" s="1"/>
-      <c r="AF3" s="1"/>
-      <c r="AG3" s="1"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="3"/>
+      <c r="AG3" s="3"/>
     </row>
-    <row r="4" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
+    <row r="4" spans="1:91" ht="27.75" thickTop="1" thickBot="1">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
       <c r="U4" s="3"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
-      <c r="Z4" s="1"/>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="1"/>
-      <c r="AC4" s="1"/>
-      <c r="AD4" s="1"/>
-      <c r="AE4" s="1"/>
-      <c r="AF4" s="1"/>
-      <c r="AG4" s="1"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="3"/>
+      <c r="AF4" s="3"/>
+      <c r="AG4" s="3"/>
     </row>
-    <row r="5" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
+    <row r="5" spans="1:91" ht="27.75" thickTop="1" thickBot="1">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-      <c r="T5" s="1"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
       <c r="U5" s="3"/>
-      <c r="V5" s="1"/>
-      <c r="W5" s="1"/>
-      <c r="X5" s="1"/>
-      <c r="Y5" s="1"/>
-      <c r="Z5" s="1"/>
-      <c r="AA5" s="1"/>
-      <c r="AB5" s="1"/>
-      <c r="AC5" s="1"/>
-      <c r="AD5" s="1"/>
-      <c r="AE5" s="1"/>
-      <c r="AF5" s="1"/>
-      <c r="AG5" s="1"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="3"/>
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
+      <c r="AB5" s="3"/>
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="3"/>
+      <c r="AE5" s="3"/>
+      <c r="AF5" s="3"/>
+      <c r="AG5" s="3"/>
     </row>
-    <row r="6" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
+    <row r="6" spans="1:91" ht="27.75" thickTop="1" thickBot="1">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
       <c r="C6" s="3"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
       <c r="U6" s="3"/>
-      <c r="V6" s="1"/>
-      <c r="W6" s="1"/>
-      <c r="X6" s="1"/>
-      <c r="Y6" s="1"/>
-      <c r="Z6" s="1"/>
-      <c r="AA6" s="1"/>
-      <c r="AB6" s="1"/>
-      <c r="AC6" s="1"/>
-      <c r="AD6" s="1"/>
-      <c r="AE6" s="1"/>
-      <c r="AF6" s="1"/>
-      <c r="AG6" s="1"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
+      <c r="AB6" s="3"/>
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="3"/>
+      <c r="AE6" s="3"/>
+      <c r="AF6" s="3"/>
+      <c r="AG6" s="3"/>
     </row>
-    <row r="7" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
+    <row r="7" spans="1:91" ht="27.75" thickTop="1" thickBot="1">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
       <c r="C7" s="3"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
-      <c r="T7" s="1"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
       <c r="U7" s="3"/>
-      <c r="V7" s="1"/>
-      <c r="W7" s="1"/>
-      <c r="X7" s="1"/>
-      <c r="Y7" s="1"/>
-      <c r="Z7" s="1"/>
-      <c r="AA7" s="1"/>
-      <c r="AB7" s="1"/>
-      <c r="AC7" s="1"/>
-      <c r="AD7" s="1"/>
-      <c r="AE7" s="1"/>
-      <c r="AF7" s="1"/>
-      <c r="AG7" s="1"/>
+      <c r="V7" s="3"/>
+      <c r="W7" s="3"/>
+      <c r="X7" s="3"/>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
+      <c r="AB7" s="3"/>
+      <c r="AC7" s="3"/>
+      <c r="AD7" s="3"/>
+      <c r="AE7" s="3"/>
+      <c r="AF7" s="3"/>
+      <c r="AG7" s="3"/>
     </row>
-    <row r="8" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
+    <row r="8" spans="1:91" ht="27.75" thickTop="1" thickBot="1">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
       <c r="C8" s="3"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
       <c r="U8" s="3"/>
-      <c r="V8" s="1"/>
-      <c r="W8" s="1"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="1"/>
-      <c r="Z8" s="1"/>
-      <c r="AA8" s="1"/>
-      <c r="AB8" s="1"/>
-      <c r="AC8" s="1"/>
-      <c r="AD8" s="1"/>
-      <c r="AE8" s="1"/>
-      <c r="AF8" s="1"/>
-      <c r="AG8" s="1"/>
+      <c r="V8" s="3"/>
+      <c r="W8" s="3"/>
+      <c r="X8" s="3"/>
+      <c r="Y8" s="3"/>
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
+      <c r="AB8" s="3"/>
+      <c r="AC8" s="3"/>
+      <c r="AD8" s="3"/>
+      <c r="AE8" s="3"/>
+      <c r="AF8" s="3"/>
+      <c r="AG8" s="3"/>
     </row>
-    <row r="9" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
+    <row r="9" spans="1:91" ht="27.75" thickTop="1" thickBot="1">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
       <c r="C9" s="3"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
       <c r="U9" s="3"/>
-      <c r="V9" s="1"/>
-      <c r="W9" s="1"/>
-      <c r="X9" s="1"/>
-      <c r="Y9" s="1"/>
-      <c r="Z9" s="1"/>
-      <c r="AA9" s="1"/>
-      <c r="AB9" s="1"/>
-      <c r="AC9" s="1"/>
-      <c r="AD9" s="1"/>
-      <c r="AE9" s="1"/>
-      <c r="AF9" s="1"/>
-      <c r="AG9" s="1"/>
+      <c r="V9" s="3"/>
+      <c r="W9" s="3"/>
+      <c r="X9" s="3"/>
+      <c r="Y9" s="3"/>
+      <c r="Z9" s="3"/>
+      <c r="AA9" s="3"/>
+      <c r="AB9" s="3"/>
+      <c r="AC9" s="3"/>
+      <c r="AD9" s="3"/>
+      <c r="AE9" s="3"/>
+      <c r="AF9" s="3"/>
+      <c r="AG9" s="3"/>
     </row>
-    <row r="10" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
+    <row r="10" spans="1:91" ht="27.75" thickTop="1" thickBot="1">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
       <c r="C10" s="3"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
-      <c r="T10" s="1"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
       <c r="U10" s="3"/>
-      <c r="V10" s="1"/>
-      <c r="W10" s="1"/>
-      <c r="X10" s="1"/>
-      <c r="Y10" s="1"/>
-      <c r="Z10" s="1"/>
-      <c r="AA10" s="1"/>
-      <c r="AB10" s="1"/>
-      <c r="AC10" s="1"/>
-      <c r="AD10" s="1"/>
-      <c r="AE10" s="1"/>
-      <c r="AF10" s="1"/>
-      <c r="AG10" s="1"/>
+      <c r="V10" s="3"/>
+      <c r="W10" s="3"/>
+      <c r="X10" s="3"/>
+      <c r="Y10" s="3"/>
+      <c r="Z10" s="3"/>
+      <c r="AA10" s="3"/>
+      <c r="AB10" s="3"/>
+      <c r="AC10" s="3"/>
+      <c r="AD10" s="3"/>
+      <c r="AE10" s="3"/>
+      <c r="AF10" s="3"/>
+      <c r="AG10" s="3"/>
     </row>
-    <row r="11" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
+    <row r="11" spans="1:91" ht="27.75" thickTop="1" thickBot="1">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
       <c r="C11" s="3"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-      <c r="V11" s="1"/>
-      <c r="W11" s="1"/>
-      <c r="X11" s="1"/>
-      <c r="Y11" s="1"/>
-      <c r="Z11" s="1"/>
-      <c r="AA11" s="1"/>
-      <c r="AB11" s="1"/>
-      <c r="AC11" s="1"/>
-      <c r="AD11" s="1"/>
-      <c r="AE11" s="1"/>
-      <c r="AF11" s="1"/>
-      <c r="AG11" s="1"/>
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
     </row>
-    <row r="12" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
+    <row r="12" spans="1:91" ht="27.75" thickTop="1" thickBot="1">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
-      <c r="S12" s="1"/>
-      <c r="T12" s="1"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
       <c r="U12" s="3"/>
-      <c r="V12" s="1"/>
-      <c r="W12" s="1"/>
-      <c r="X12" s="1"/>
-      <c r="Y12" s="1"/>
-      <c r="Z12" s="1"/>
-      <c r="AA12" s="1"/>
-      <c r="AB12" s="1"/>
-      <c r="AC12" s="1"/>
-      <c r="AD12" s="1"/>
-      <c r="AE12" s="1"/>
-      <c r="AF12" s="1"/>
-      <c r="AG12" s="1"/>
+      <c r="V12" s="3"/>
+      <c r="W12" s="3"/>
+      <c r="X12" s="3"/>
+      <c r="Y12" s="3"/>
+      <c r="Z12" s="3"/>
+      <c r="AA12" s="3"/>
+      <c r="AB12" s="3"/>
+      <c r="AC12" s="3"/>
+      <c r="AD12" s="3"/>
+      <c r="AE12" s="3"/>
+      <c r="AF12" s="3"/>
+      <c r="AG12" s="3"/>
     </row>
-    <row r="13" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
+    <row r="13" spans="1:91" ht="27.75" thickTop="1" thickBot="1">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
       <c r="C13" s="3"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
-      <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
-      <c r="T13" s="1"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
       <c r="U13" s="3"/>
-      <c r="V13" s="1"/>
-      <c r="W13" s="1"/>
-      <c r="X13" s="1"/>
-      <c r="Y13" s="1"/>
-      <c r="Z13" s="1"/>
-      <c r="AA13" s="1"/>
-      <c r="AB13" s="1"/>
-      <c r="AC13" s="1"/>
-      <c r="AD13" s="1"/>
-      <c r="AE13" s="1"/>
-      <c r="AF13" s="1"/>
-      <c r="AG13" s="1"/>
+      <c r="V13" s="3"/>
+      <c r="W13" s="3"/>
+      <c r="X13" s="3"/>
+      <c r="Y13" s="3"/>
+      <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
+      <c r="AB13" s="3"/>
+      <c r="AC13" s="3"/>
+      <c r="AD13" s="3"/>
+      <c r="AE13" s="3"/>
+      <c r="AF13" s="3"/>
+      <c r="AG13" s="3"/>
     </row>
-    <row r="14" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
+    <row r="14" spans="1:91" ht="27.75" thickTop="1" thickBot="1">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
       <c r="C14" s="3"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
-      <c r="S14" s="1"/>
-      <c r="T14" s="1"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
       <c r="U14" s="3"/>
-      <c r="V14" s="1"/>
-      <c r="W14" s="1"/>
-      <c r="X14" s="1"/>
-      <c r="Y14" s="1"/>
-      <c r="Z14" s="1"/>
-      <c r="AA14" s="1"/>
-      <c r="AB14" s="1"/>
-      <c r="AC14" s="1"/>
-      <c r="AD14" s="1"/>
-      <c r="AE14" s="1"/>
-      <c r="AF14" s="1"/>
-      <c r="AG14" s="1"/>
+      <c r="V14" s="3"/>
+      <c r="W14" s="3"/>
+      <c r="X14" s="3"/>
+      <c r="Y14" s="3"/>
+      <c r="Z14" s="3"/>
+      <c r="AA14" s="3"/>
+      <c r="AB14" s="3"/>
+      <c r="AC14" s="3"/>
+      <c r="AD14" s="3"/>
+      <c r="AE14" s="3"/>
+      <c r="AF14" s="3"/>
+      <c r="AG14" s="3"/>
     </row>
-    <row r="15" spans="1:33" ht="27" thickTop="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
+    <row r="15" spans="1:91" ht="27" thickTop="1">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
       <c r="C15" s="3"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
-      <c r="R15" s="1"/>
-      <c r="S15" s="1"/>
-      <c r="T15" s="1"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
       <c r="U15" s="3"/>
-      <c r="V15" s="1"/>
-      <c r="W15" s="1"/>
-      <c r="X15" s="1"/>
-      <c r="Y15" s="1"/>
-      <c r="Z15" s="1"/>
-      <c r="AA15" s="1"/>
-      <c r="AB15" s="1"/>
-      <c r="AC15" s="1"/>
-      <c r="AD15" s="1"/>
-      <c r="AE15" s="1"/>
-      <c r="AF15" s="1"/>
-      <c r="AG15" s="1"/>
+      <c r="V15" s="3"/>
+      <c r="W15" s="3"/>
+      <c r="X15" s="3"/>
+      <c r="Y15" s="3"/>
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
+      <c r="AB15" s="3"/>
+      <c r="AC15" s="3"/>
+      <c r="AD15" s="3"/>
+      <c r="AE15" s="3"/>
+      <c r="AF15" s="3"/>
+      <c r="AG15" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AG1" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AE86">
+  <autoFilter ref="A1:AG1">
+    <sortState ref="A2:AE86">
       <sortCondition ref="C1"/>
     </sortState>
   </autoFilter>

--- a/importationFileUpload/Template-Ar.xlsx
+++ b/importationFileUpload/Template-Ar.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moknial01\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Moknine Ahmed\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -27,128 +27,23 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
   <si>
     <t>العدد</t>
   </si>
   <si>
-    <t>رقـــم 
-الملــــــف</t>
-  </si>
-  <si>
-    <t>تاريــــخ 
-الايـــداع</t>
-  </si>
-  <si>
-    <t>اللقــــب</t>
-  </si>
-  <si>
-    <t>الاســــم</t>
-  </si>
-  <si>
     <t>الجنس</t>
   </si>
   <si>
     <t>تاريخ الميلاد</t>
   </si>
   <si>
-    <t>رقـم عقد الميـــــلاد</t>
-  </si>
-  <si>
-    <t>بلــدية الميــــلاد</t>
-  </si>
-  <si>
     <t>الحالة العائلية</t>
   </si>
   <si>
-    <t>اســــــــم الاب</t>
-  </si>
-  <si>
-    <t>لقــــــب الام</t>
-  </si>
-  <si>
-    <t>اســــم الام</t>
-  </si>
-  <si>
-    <t>العنـــــــــــــــــــــــــــــــــــــــــوان</t>
-  </si>
-  <si>
-    <t>لقـــب الــزوج(ة)</t>
-  </si>
-  <si>
-    <t>تاريـخ ميـــلاد
- الـــــــــزوج (ة)</t>
-  </si>
-  <si>
-    <t>رقم عقد ميلاد الـــزوج(ة)</t>
-  </si>
-  <si>
-    <t>بلـــدية ميــــــلاد الـــــــــــــزوج(ة)</t>
-  </si>
-  <si>
-    <t>اســم أم الـــــزوج (ة)</t>
-  </si>
-  <si>
-    <t>لقـــب أم الــزوج(ة)</t>
-  </si>
-  <si>
     <t>المجموع</t>
   </si>
   <si>
-    <t>الملاحظـــــــــــــــــــــــــــة</t>
-  </si>
-  <si>
-    <r>
-      <t>اســــم 
-الـــزوج(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
-        <color indexed="10"/>
-        <rFont val="Mohammad Bold Normal"/>
-        <charset val="178"/>
-      </rPr>
-      <t>ة</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
-        <color indexed="8"/>
-        <rFont val="Mohammad Bold Normal"/>
-        <charset val="178"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>اســـــــم أب الـــــزوج(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
-        <color indexed="10"/>
-        <rFont val="Mohammad Bold Normal"/>
-        <charset val="178"/>
-      </rPr>
-      <t>ة</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
-        <color indexed="8"/>
-        <rFont val="Mohammad Bold Normal"/>
-        <charset val="178"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
     <t>عدد الزوجات</t>
   </si>
   <si>
@@ -171,6 +66,78 @@
   </si>
   <si>
     <t>رقم التعريف الوطني</t>
+  </si>
+  <si>
+    <t>رقم الملف</t>
+  </si>
+  <si>
+    <t>تاريخ الايداع</t>
+  </si>
+  <si>
+    <t>رقم عقد الميلاد</t>
+  </si>
+  <si>
+    <t>بلدية الميلاد</t>
+  </si>
+  <si>
+    <t>اسم الاب</t>
+  </si>
+  <si>
+    <t>لقب الام</t>
+  </si>
+  <si>
+    <t>اسم الام</t>
+  </si>
+  <si>
+    <t>اسم الزوج(ة)</t>
+  </si>
+  <si>
+    <t>لقب الزوج(ة)</t>
+  </si>
+  <si>
+    <t>تاريخ ميلاد الزوج(ة)</t>
+  </si>
+  <si>
+    <t>رقم عقد ميلاد الزوج(ة)</t>
+  </si>
+  <si>
+    <t>بلدية ميلاد الزوج(ة)</t>
+  </si>
+  <si>
+    <t>اسم أب الزوج(ة)</t>
+  </si>
+  <si>
+    <t>اسم أم الزوج(ة)</t>
+  </si>
+  <si>
+    <t>لقب أم الزوج(ة)</t>
+  </si>
+  <si>
+    <t>الملاحظة</t>
+  </si>
+  <si>
+    <t>العنوان</t>
+  </si>
+  <si>
+    <t>ee</t>
+  </si>
+  <si>
+    <t>ff</t>
+  </si>
+  <si>
+    <t>لبفب</t>
+  </si>
+  <si>
+    <t>منمن</t>
+  </si>
+  <si>
+    <t>ثسثس</t>
+  </si>
+  <si>
+    <t>اللقب</t>
+  </si>
+  <si>
+    <t>الاسم</t>
   </si>
 </sst>
 </file>
@@ -180,7 +147,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -240,20 +207,6 @@
       <b/>
       <sz val="20"/>
       <color rgb="FF008000"/>
-      <name val="Mohammad Bold Normal"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color indexed="10"/>
-      <name val="Mohammad Bold Normal"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color indexed="8"/>
       <name val="Mohammad Bold Normal"/>
       <charset val="178"/>
     </font>
@@ -374,7 +327,7 @@
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
@@ -393,19 +346,19 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Currency" xfId="5"/>
@@ -698,7 +651,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:CM15"/>
+  <dimension ref="A1:AG15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
@@ -733,113 +686,123 @@
     <col min="33" max="33" width="47.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:91" s="1" customFormat="1" ht="54" thickTop="1" thickBot="1">
+    <row r="1" spans="1:33" s="1" customFormat="1" ht="54" thickTop="1" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="G1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="H1" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="M1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="V1" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="W1" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="X1" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC1" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="6" t="s">
+      <c r="AG1" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" s="12" customFormat="1" ht="27.75" thickTop="1" thickBot="1">
+      <c r="A2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="3">
+        <v>3456</v>
+      </c>
+      <c r="C2" s="3">
         <v>6</v>
       </c>
-      <c r="H1" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="T1" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="U1" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="V1" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="W1" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="X1" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="Y1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z1" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB1" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC1" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD1" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="AF1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG1" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:91" s="12" customFormat="1" ht="27.75" thickTop="1" thickBot="1">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
+      <c r="D2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -868,71 +831,21 @@
       <c r="AE2" s="3"/>
       <c r="AF2" s="3"/>
       <c r="AG2" s="3"/>
-      <c r="AH2" s="1"/>
-      <c r="AI2" s="1"/>
-      <c r="AJ2" s="1"/>
-      <c r="AK2" s="1"/>
-      <c r="AL2" s="1"/>
-      <c r="AM2" s="1"/>
-      <c r="AN2" s="1"/>
-      <c r="AO2" s="1"/>
-      <c r="AP2" s="1"/>
-      <c r="AQ2" s="1"/>
-      <c r="AR2" s="1"/>
-      <c r="AS2" s="1"/>
-      <c r="AT2" s="1"/>
-      <c r="AU2" s="1"/>
-      <c r="AV2" s="1"/>
-      <c r="AW2" s="1"/>
-      <c r="AX2" s="1"/>
-      <c r="AY2" s="1"/>
-      <c r="AZ2" s="1"/>
-      <c r="BA2" s="1"/>
-      <c r="BB2" s="1"/>
-      <c r="BC2" s="1"/>
-      <c r="BD2" s="1"/>
-      <c r="BE2" s="1"/>
-      <c r="BF2" s="1"/>
-      <c r="BG2" s="1"/>
-      <c r="BH2" s="1"/>
-      <c r="BI2" s="1"/>
-      <c r="BJ2" s="1"/>
-      <c r="BK2" s="1"/>
-      <c r="BL2" s="1"/>
-      <c r="BM2" s="1"/>
-      <c r="BN2" s="1"/>
-      <c r="BO2" s="1"/>
-      <c r="BP2" s="1"/>
-      <c r="BQ2" s="1"/>
-      <c r="BR2" s="1"/>
-      <c r="BS2" s="1"/>
-      <c r="BT2" s="1"/>
-      <c r="BU2" s="1"/>
-      <c r="BV2" s="1"/>
-      <c r="BW2" s="1"/>
-      <c r="BX2" s="1"/>
-      <c r="BY2" s="1"/>
-      <c r="BZ2" s="1"/>
-      <c r="CA2" s="1"/>
-      <c r="CB2" s="1"/>
-      <c r="CC2" s="1"/>
-      <c r="CD2" s="1"/>
-      <c r="CE2" s="1"/>
-      <c r="CF2" s="1"/>
-      <c r="CG2" s="1"/>
-      <c r="CH2" s="1"/>
-      <c r="CI2" s="1"/>
-      <c r="CJ2" s="1"/>
-      <c r="CK2" s="1"/>
-      <c r="CL2" s="1"/>
-      <c r="CM2" s="1"/>
-    </row>
-    <row r="3" spans="1:91" ht="27.75" thickTop="1" thickBot="1">
+    </row>
+    <row r="3" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
       <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+      <c r="B3" s="3">
+        <v>44</v>
+      </c>
+      <c r="C3" s="3">
+        <v>5</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -962,10 +875,14 @@
       <c r="AF3" s="3"/>
       <c r="AG3" s="3"/>
     </row>
-    <row r="4" spans="1:91" ht="27.75" thickTop="1" thickBot="1">
+    <row r="4" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
       <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
+      <c r="B4" s="3">
+        <v>55</v>
+      </c>
+      <c r="C4" s="3">
+        <v>6</v>
+      </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -997,12 +914,20 @@
       <c r="AF4" s="3"/>
       <c r="AG4" s="3"/>
     </row>
-    <row r="5" spans="1:91" ht="27.75" thickTop="1" thickBot="1">
+    <row r="5" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
       <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
+      <c r="B5" s="3">
+        <v>66</v>
+      </c>
+      <c r="C5" s="3">
+        <v>5</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -1032,7 +957,7 @@
       <c r="AF5" s="3"/>
       <c r="AG5" s="3"/>
     </row>
-    <row r="6" spans="1:91" ht="27.75" thickTop="1" thickBot="1">
+    <row r="6" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -1067,7 +992,7 @@
       <c r="AF6" s="3"/>
       <c r="AG6" s="3"/>
     </row>
-    <row r="7" spans="1:91" ht="27.75" thickTop="1" thickBot="1">
+    <row r="7" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -1102,7 +1027,7 @@
       <c r="AF7" s="3"/>
       <c r="AG7" s="3"/>
     </row>
-    <row r="8" spans="1:91" ht="27.75" thickTop="1" thickBot="1">
+    <row r="8" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1137,7 +1062,7 @@
       <c r="AF8" s="3"/>
       <c r="AG8" s="3"/>
     </row>
-    <row r="9" spans="1:91" ht="27.75" thickTop="1" thickBot="1">
+    <row r="9" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -1172,7 +1097,7 @@
       <c r="AF9" s="3"/>
       <c r="AG9" s="3"/>
     </row>
-    <row r="10" spans="1:91" ht="27.75" thickTop="1" thickBot="1">
+    <row r="10" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -1207,7 +1132,7 @@
       <c r="AF10" s="3"/>
       <c r="AG10" s="3"/>
     </row>
-    <row r="11" spans="1:91" ht="27.75" thickTop="1" thickBot="1">
+    <row r="11" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -1242,7 +1167,7 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
     </row>
-    <row r="12" spans="1:91" ht="27.75" thickTop="1" thickBot="1">
+    <row r="12" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -1277,7 +1202,7 @@
       <c r="AF12" s="3"/>
       <c r="AG12" s="3"/>
     </row>
-    <row r="13" spans="1:91" ht="27.75" thickTop="1" thickBot="1">
+    <row r="13" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1312,7 +1237,7 @@
       <c r="AF13" s="3"/>
       <c r="AG13" s="3"/>
     </row>
-    <row r="14" spans="1:91" ht="27.75" thickTop="1" thickBot="1">
+    <row r="14" spans="1:33" ht="27.75" thickTop="1" thickBot="1">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1347,7 +1272,7 @@
       <c r="AF14" s="3"/>
       <c r="AG14" s="3"/>
     </row>
-    <row r="15" spans="1:91" ht="27" thickTop="1">
+    <row r="15" spans="1:33" ht="27" thickTop="1">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
